--- a/App/dataset/planets_dataset.xlsx
+++ b/App/dataset/planets_dataset.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elyon\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elyon\OneDrive\Desktop\phd_PE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA486804-B39E-49AC-9555-024032C99851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A85C38D-9EC3-4424-8EEB-2350792E09ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F6D54169-1D24-43BA-8B71-94708FE87452}"/>
   </bookViews>
@@ -268,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -311,6 +311,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -751,10 +754,10 @@
       <c r="K2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="16">
         <v>1.98842E+30</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="13">
         <v>132712000000</v>
       </c>
       <c r="N2" s="7">

--- a/App/dataset/planets_dataset.xlsx
+++ b/App/dataset/planets_dataset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elyon\OneDrive\Desktop\phd_PE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elyon\OneDrive\Desktop\Cosmo-Edu_Lab\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A85C38D-9EC3-4424-8EEB-2350792E09ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583CBD93-90BA-4A3B-8DCF-C63A30A480D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F6D54169-1D24-43BA-8B71-94708FE87452}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
-  <si>
-    <t>Celestial_Body</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>SemiMajorAxis(km)</t>
   </si>
@@ -74,9 +71,6 @@
     <t>Mass(kg)</t>
   </si>
   <si>
-    <t>GM(km3/s2)</t>
-  </si>
-  <si>
     <t>MassFraction_SolarSystem</t>
   </si>
   <si>
@@ -116,23 +110,122 @@
     <t>Pluto</t>
   </si>
   <si>
-    <t>G</t>
-  </si>
-  <si>
     <t>CONSTANTS</t>
   </si>
   <si>
-    <t>VelocityFormula</t>
-  </si>
-  <si>
-    <t>radq(G*M_sun/d)</t>
+    <r>
+      <t>G(N*m</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/kg</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  )</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GM(km</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/s</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Celestial Body</t>
+  </si>
+  <si>
+    <t>Velocity Formula</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,6 +253,24 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -268,7 +379,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -311,9 +422,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -650,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9A7422D-AF62-462E-97FE-01E084A0D0D7}">
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.109375" customWidth="1"/>
@@ -670,48 +778,48 @@
     <col min="15" max="15" width="23.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="O1" s="12" t="s">
         <v>28</v>
@@ -722,7 +830,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B2" s="6">
         <v>0</v>
@@ -746,15 +854,15 @@
         <v>0</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J2" s="6">
         <v>695700</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="16">
+        <v>13</v>
+      </c>
+      <c r="L2" s="7">
         <v>1.98842E+30</v>
       </c>
       <c r="M2" s="13">
@@ -763,16 +871,14 @@
       <c r="N2" s="7">
         <v>0.99865700000000002</v>
       </c>
-      <c r="O2" s="15" t="s">
-        <v>29</v>
-      </c>
+      <c r="O2" s="15"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B3" s="7">
         <v>57909100</v>
@@ -820,7 +926,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4" s="7">
         <v>108209000</v>
@@ -868,7 +974,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5" s="7">
         <v>149598000</v>
@@ -916,46 +1022,46 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="7">
-        <v>383398</v>
+        <v>227939000</v>
       </c>
       <c r="C6" s="7">
-        <v>362106</v>
+        <v>206645000</v>
       </c>
       <c r="D6" s="7">
-        <v>404689</v>
+        <v>249233000</v>
       </c>
       <c r="E6" s="6">
-        <v>27.18</v>
+        <v>686.97</v>
       </c>
       <c r="F6" s="6">
-        <v>1.03</v>
+        <v>24.13</v>
       </c>
       <c r="G6" s="6">
-        <v>5.5550000000000002E-2</v>
+        <v>9.3420000000000003E-2</v>
       </c>
       <c r="H6" s="6">
-        <v>23.71</v>
+        <v>1.85</v>
       </c>
       <c r="I6" s="6">
-        <v>1737.4</v>
+        <v>3389.5</v>
       </c>
       <c r="J6" s="6">
-        <v>1737.4</v>
+        <v>3396.19</v>
       </c>
       <c r="K6" s="6">
-        <v>1737.4</v>
+        <v>3376.2</v>
       </c>
       <c r="L6" s="7">
-        <v>7.3458099999999999E+22</v>
+        <v>6.4169299999999999E+23</v>
       </c>
       <c r="M6" s="7">
-        <v>4902.8</v>
+        <v>42828.4</v>
       </c>
       <c r="N6" s="7">
-        <v>3.68934E-8</v>
+        <v>3.22282E-7</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="4"/>
@@ -964,46 +1070,46 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="7">
-        <v>227939000</v>
+        <v>778321000</v>
       </c>
       <c r="C7" s="7">
-        <v>206645000</v>
+        <v>740603000</v>
       </c>
       <c r="D7" s="7">
-        <v>249233000</v>
+        <v>816038000</v>
       </c>
       <c r="E7" s="6">
-        <v>686.97</v>
+        <v>4332.5200000000004</v>
       </c>
       <c r="F7" s="6">
-        <v>24.13</v>
+        <v>13.06</v>
       </c>
       <c r="G7" s="6">
-        <v>9.3420000000000003E-2</v>
+        <v>4.8460000000000003E-2</v>
       </c>
       <c r="H7" s="6">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="I7" s="6">
-        <v>3389.5</v>
+        <v>69911</v>
       </c>
       <c r="J7" s="6">
-        <v>3396.19</v>
+        <v>71492</v>
       </c>
       <c r="K7" s="6">
-        <v>3376.2</v>
+        <v>66854</v>
       </c>
       <c r="L7" s="7">
-        <v>6.4169299999999999E+23</v>
+        <v>1.89852E+27</v>
       </c>
       <c r="M7" s="7">
-        <v>42828.4</v>
+        <v>126713000</v>
       </c>
       <c r="N7" s="7">
-        <v>3.22282E-7</v>
+        <v>9.5350999999999997E-4</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="4"/>
@@ -1012,46 +1118,46 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" s="7">
-        <v>778321000</v>
+        <v>1429100000</v>
       </c>
       <c r="C8" s="7">
-        <v>740603000</v>
+        <v>1350960000</v>
       </c>
       <c r="D8" s="7">
-        <v>816038000</v>
+        <v>1507240000</v>
       </c>
       <c r="E8" s="6">
-        <v>4332.5200000000004</v>
+        <v>10783.05</v>
       </c>
       <c r="F8" s="6">
-        <v>13.06</v>
+        <v>9.64</v>
       </c>
       <c r="G8" s="6">
-        <v>4.8460000000000003E-2</v>
+        <v>5.4679999999999999E-2</v>
       </c>
       <c r="H8" s="6">
-        <v>1.3</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="I8" s="6">
-        <v>69911</v>
+        <v>58232</v>
       </c>
       <c r="J8" s="6">
-        <v>71492</v>
+        <v>60268</v>
       </c>
       <c r="K8" s="6">
-        <v>66854</v>
+        <v>54364</v>
       </c>
       <c r="L8" s="7">
-        <v>1.89852E+27</v>
+        <v>5.6846000000000003E+26</v>
       </c>
       <c r="M8" s="7">
-        <v>126713000</v>
+        <v>37940600</v>
       </c>
       <c r="N8" s="7">
-        <v>9.5350999999999997E-4</v>
+        <v>2.8550199999999998E-4</v>
       </c>
       <c r="O8" s="6"/>
       <c r="P8" s="4"/>
@@ -1060,46 +1166,46 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" s="7">
-        <v>1429100000</v>
+        <v>2874790000</v>
       </c>
       <c r="C9" s="7">
-        <v>1350960000</v>
+        <v>2738540000</v>
       </c>
       <c r="D9" s="7">
-        <v>1507240000</v>
+        <v>3011040000</v>
       </c>
       <c r="E9" s="6">
-        <v>10783.05</v>
+        <v>30768.84</v>
       </c>
       <c r="F9" s="6">
-        <v>9.64</v>
+        <v>6.79</v>
       </c>
       <c r="G9" s="6">
-        <v>5.4679999999999999E-2</v>
+        <v>4.7390000000000002E-2</v>
       </c>
       <c r="H9" s="6">
-        <v>2.4900000000000002</v>
+        <v>0.77</v>
       </c>
       <c r="I9" s="6">
-        <v>58232</v>
+        <v>25362</v>
       </c>
       <c r="J9" s="6">
-        <v>60268</v>
+        <v>25559</v>
       </c>
       <c r="K9" s="6">
-        <v>54364</v>
+        <v>24973</v>
       </c>
       <c r="L9" s="7">
-        <v>5.6846000000000003E+26</v>
+        <v>8.6819200000000008E+25</v>
       </c>
       <c r="M9" s="7">
-        <v>37940600</v>
+        <v>5794560</v>
       </c>
       <c r="N9" s="7">
-        <v>2.8550199999999998E-4</v>
+        <v>4.3603899999999998E-5</v>
       </c>
       <c r="O9" s="6"/>
       <c r="P9" s="4"/>
@@ -1108,46 +1214,46 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" s="7">
-        <v>2874790000</v>
+        <v>4504890000</v>
       </c>
       <c r="C10" s="7">
-        <v>2738540000</v>
+        <v>4463840000</v>
       </c>
       <c r="D10" s="7">
-        <v>3011040000</v>
+        <v>4545940000</v>
       </c>
       <c r="E10" s="6">
-        <v>30768.84</v>
+        <v>60357.05</v>
       </c>
       <c r="F10" s="6">
-        <v>6.79</v>
+        <v>5.43</v>
       </c>
       <c r="G10" s="6">
-        <v>4.7390000000000002E-2</v>
+        <v>9.11E-3</v>
       </c>
       <c r="H10" s="6">
-        <v>0.77</v>
+        <v>1.77</v>
       </c>
       <c r="I10" s="6">
-        <v>25362</v>
+        <v>24622</v>
       </c>
       <c r="J10" s="6">
-        <v>25559</v>
+        <v>24764</v>
       </c>
       <c r="K10" s="6">
-        <v>24973</v>
+        <v>24341</v>
       </c>
       <c r="L10" s="7">
-        <v>8.6819200000000008E+25</v>
+        <v>1.02431E+26</v>
       </c>
       <c r="M10" s="7">
-        <v>5794560</v>
+        <v>6836530</v>
       </c>
       <c r="N10" s="7">
-        <v>4.3603899999999998E-5</v>
+        <v>5.1444699999999999E-5</v>
       </c>
       <c r="O10" s="6"/>
       <c r="P10" s="4"/>
@@ -1156,46 +1262,46 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="7">
-        <v>4504890000</v>
+        <v>5915400000</v>
       </c>
       <c r="C11" s="7">
-        <v>4463840000</v>
+        <v>4442120000</v>
       </c>
       <c r="D11" s="7">
-        <v>4545940000</v>
+        <v>7388680000</v>
       </c>
       <c r="E11" s="6">
-        <v>60357.05</v>
+        <v>90821.51</v>
       </c>
       <c r="F11" s="6">
-        <v>5.43</v>
+        <v>4.74</v>
       </c>
       <c r="G11" s="6">
-        <v>9.11E-3</v>
+        <v>0.24906</v>
       </c>
       <c r="H11" s="6">
-        <v>1.77</v>
+        <v>17.14</v>
       </c>
       <c r="I11" s="6">
-        <v>24622</v>
+        <v>1188.3</v>
       </c>
       <c r="J11" s="6">
-        <v>24764</v>
+        <v>1188.3</v>
       </c>
       <c r="K11" s="6">
-        <v>24341</v>
+        <v>1188.3</v>
       </c>
       <c r="L11" s="7">
-        <v>1.02431E+26</v>
+        <v>1.4615799999999999E+22</v>
       </c>
       <c r="M11" s="7">
-        <v>6836530</v>
+        <v>975.5</v>
       </c>
       <c r="N11" s="7">
-        <v>5.1444699999999999E-5</v>
+        <v>7.3406099999999999E-9</v>
       </c>
       <c r="O11" s="6"/>
       <c r="P11" s="4"/>
@@ -1204,101 +1310,101 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B12" s="7">
-        <v>5915400000</v>
+        <v>383398</v>
       </c>
       <c r="C12" s="7">
-        <v>4442120000</v>
+        <v>362106</v>
       </c>
       <c r="D12" s="7">
-        <v>7388680000</v>
+        <v>404689</v>
       </c>
       <c r="E12" s="6">
-        <v>90821.51</v>
+        <v>27.18</v>
       </c>
       <c r="F12" s="6">
-        <v>4.74</v>
+        <v>1.03</v>
       </c>
       <c r="G12" s="6">
-        <v>0.24906</v>
+        <v>5.5550000000000002E-2</v>
       </c>
       <c r="H12" s="6">
-        <v>17.14</v>
+        <v>23.71</v>
       </c>
       <c r="I12" s="6">
-        <v>1188.3</v>
+        <v>1737.4</v>
       </c>
       <c r="J12" s="6">
-        <v>1188.3</v>
+        <v>1737.4</v>
       </c>
       <c r="K12" s="6">
-        <v>1188.3</v>
+        <v>1737.4</v>
       </c>
       <c r="L12" s="7">
-        <v>1.4615799999999999E+22</v>
+        <v>7.3458099999999999E+22</v>
       </c>
       <c r="M12" s="7">
-        <v>975.5</v>
+        <v>4902.8</v>
       </c>
       <c r="N12" s="7">
-        <v>7.3406099999999999E-9</v>
+        <v>3.68934E-8</v>
       </c>
       <c r="O12" s="6"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-    </row>
-    <row r="14" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
+    <row r="13" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="11">
+        <v>6.67E-11</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="11">
-        <v>6.67E-11</v>
-      </c>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -1436,26 +1542,6 @@
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
